--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -1,61 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arrivagroup-my.sharepoint.com/personal/sokvari_norbert_arrivabus_hu/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{20A3A44A-1C72-419D-A466-81D0CDE1E262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C513D8F-0E12-46F2-B3F4-099D6FA8A20D}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="18900" windowWidth="21600" windowHeight="11295" xr2:uid="{4AD81AF9-0199-4ABD-8C88-E50CAFDA8178}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4140" yWindow="18900" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Riport" sheetId="1" r:id="rId1"/>
+    <sheet name="Riport" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -70,22 +60,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -405,10 +456,572 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E3412-B789-441D-B168-440C0DF764A6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Dátum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Viszonylat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Forda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rendszám</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Eredmény</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>RENDBEN TÁROLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>RENDBEN TÁROLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>RENDBEN TÁROLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PDN609</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>RENDBEN TÁROLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AAHY805</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,9 @@
         <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid"/>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,10 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -461,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -514,7 +518,6 @@
           <t>59</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -564,7 +567,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -587,7 +589,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -799,7 +800,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -822,7 +822,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -845,7 +844,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -895,7 +893,6 @@
           <t>58</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -945,7 +942,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -968,7 +964,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -991,7 +986,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
@@ -1014,10 +1008,532 @@
           <t>22</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="inlineStr">
         <is>
           <t>ELTÉRÉS TÖRTÉNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PDN609</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AAHY805</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>???</t>
         </is>
       </c>
     </row>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -1,61 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arrivagroup-my.sharepoint.com/personal/sokvari_norbert_arrivabus_hu/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{20A3A44A-1C72-419D-A466-81D0CDE1E262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C513D8F-0E12-46F2-B3F4-099D6FA8A20D}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="18900" windowWidth="21600" windowHeight="11295" xr2:uid="{4AD81AF9-0199-4ABD-8C88-E50CAFDA8178}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4140" yWindow="18900" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Riport" sheetId="1" r:id="rId1"/>
+    <sheet name="Riport" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -70,22 +60,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -405,10 +456,616 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E3412-B789-441D-B168-440C0DF764A6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Dátum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Viszonylat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Forda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rendszám</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Eredmény</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGY807</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PDN609</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AAHY824</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AAHY805</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -1,46 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arrivagroup-my.sharepoint.com/personal/sokvari_norbert_arrivabus_hu/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{374390BC-C7DD-4176-949D-C8C47678D419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B39F27CF-6D5E-48A6-8FE2-AEDF0B3E1F9D}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Riport" sheetId="1" r:id="rId1"/>
+    <sheet name="Riport" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,22 +60,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -390,16 +456,616 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Dátum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Viszonylat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Forda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rendszám</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Eredmény</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGY809</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AOGF779</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AOGF780</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AAHY805</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>+++</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -1,46 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arrivagroup-my.sharepoint.com/personal/sokvari_norbert_arrivabus_hu/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{374390BC-C7DD-4176-949D-C8C47678D419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B39F27CF-6D5E-48A6-8FE2-AEDF0B3E1F9D}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Riport" sheetId="1" r:id="rId1"/>
+    <sheet name="Riport" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,22 +60,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -390,16 +456,616 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Dátum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Viszonylat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Forda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rendszám</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Eredmény</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PDN627</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AOGF779</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AAHY805</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AOIM019</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -1,46 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arrivagroup-my.sharepoint.com/personal/sokvari_norbert_arrivabus_hu/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{374390BC-C7DD-4176-949D-C8C47678D419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B39F27CF-6D5E-48A6-8FE2-AEDF0B3E1F9D}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Riport" sheetId="1" r:id="rId1"/>
+    <sheet name="Riport" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,22 +60,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -390,16 +456,727 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Dátum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Viszonylat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Forda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rendszám</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Eredmény</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Tárolás helye</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AAHY866</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AOIM021</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -469,7 +469,8 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,7 +501,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Tárolás helye</t>
+          <t>Terv tárolás</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Tény tárolás</t>
         </is>
       </c>
     </row>
@@ -530,7 +536,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Békásmegyer</t>
         </is>
@@ -562,7 +573,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Békásmegyer</t>
         </is>
@@ -594,7 +610,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
         </is>
@@ -626,7 +647,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
         </is>
@@ -658,7 +684,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
         </is>
@@ -690,7 +721,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
         </is>
@@ -722,7 +758,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
         </is>
@@ -754,7 +795,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
         </is>
@@ -786,7 +832,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>Kőbánya alsó</t>
         </is>
@@ -818,7 +869,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Kőbánya alsó</t>
         </is>
@@ -850,7 +906,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>Kőbánya alsó</t>
         </is>
@@ -882,7 +943,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest</t>
         </is>
@@ -914,7 +980,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest</t>
         </is>
@@ -946,7 +1017,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest</t>
         </is>
@@ -978,7 +1054,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest</t>
         </is>
@@ -1010,7 +1091,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>Mexikói út</t>
         </is>
@@ -1042,7 +1128,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>Mexikói út</t>
         </is>
@@ -1074,7 +1165,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest</t>
         </is>
@@ -1106,7 +1202,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>Pestszentlőrinc</t>
         </is>
@@ -1138,7 +1239,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>Pestszentlőrinc</t>
         </is>
@@ -1170,7 +1276,12 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>Pestszentlőrinc</t>
         </is>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -1,46 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arrivagroup-my.sharepoint.com/personal/sokvari_norbert_arrivabus_hu/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{374390BC-C7DD-4176-949D-C8C47678D419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B39F27CF-6D5E-48A6-8FE2-AEDF0B3E1F9D}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Riport" sheetId="1" r:id="rId1"/>
+    <sheet name="Riport" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,22 +60,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -390,16 +456,838 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Dátum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Viszonylat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Forda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rendszám</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Terv tárolás</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Eredmény</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Tény tárolás</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AAHY866</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AOIM021</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -1287,6 +1287,783 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AAHY805</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AOIM008</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,9 @@
         <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid"/>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,10 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -461,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -2064,6 +2068,779 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SGY816</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AAHY805</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>47.463066, 19.149382</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AOIM022</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -474,7 +474,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2491,7 +2491,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest M (Sibrik tároló)</t>
@@ -2836,6 +2835,775 @@
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AAHY805</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="inlineStr">
         <is>
           <t>Pestszentlőrinc</t>
         </is>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -3263,7 +3263,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest M (Sibrik tároló)</t>
@@ -3481,7 +3480,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Pestszentlőrinc vasútállomás</t>
@@ -3604,6 +3602,783 @@
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>PDN638</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>47.451496, 19.10856</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Bogáncs telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AAHY804</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PDN634</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>47.453785, 19.14114</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AOIM022</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="inlineStr">
         <is>
           <t>Pestszentlőrinc</t>
         </is>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -4384,6 +4384,783 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G113" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>PDN637</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>47.46277, 19.149864</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AAHY862</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>47.543865, 19.114477</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AOIM022</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AOIM011</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -5161,6 +5161,783 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PDN624</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AOJM873</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SGY804</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G135" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AOGF672</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G137" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AOIM014</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PDN622</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SGY813</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>AOJM872</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>PDN611</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>47.462814, 19.150295</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G143" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AAHY863</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F144" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G144" s="1" t="inlineStr">
+        <is>
+          <t>Mexikói út</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PDN621</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>AOGF779</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F147" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G147" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>AOIM022</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F148" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G148" s="1" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -5938,6 +5938,699 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó vasútállomás</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1820</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Mexikói út M</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc vasútállomás</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>n.a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -5954,7 +5954,6 @@
           <t>59</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Békásmegyer, Újmegyeri tér</t>
@@ -5987,7 +5986,6 @@
           <t>57</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Békásmegyer, Újmegyeri tér</t>
@@ -6020,7 +6018,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
@@ -6053,7 +6050,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
@@ -6086,7 +6082,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
@@ -6119,7 +6114,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
@@ -6152,7 +6146,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
@@ -6185,7 +6178,6 @@
           <t>34</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Csepel, Szent Imre tér</t>
@@ -6218,7 +6210,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Kőbánya alsó vasútállomás</t>
@@ -6251,7 +6242,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>Kőbánya alsó vasútállomás</t>
@@ -6284,7 +6274,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>Kőbánya alsó vasútállomás</t>
@@ -6317,7 +6306,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest M (Sibrik tároló)</t>
@@ -6350,7 +6338,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest M (Sibrik tároló)</t>
@@ -6383,7 +6370,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest M (Sibrik tároló)</t>
@@ -6416,7 +6402,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Kőbánya-Kispest M (Sibrik tároló)</t>
@@ -6449,7 +6434,6 @@
           <t>58</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>Mexikói út M</t>
@@ -6482,7 +6466,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>Mexikói út M</t>
@@ -6515,7 +6498,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>Pestszentlőrinc vasútállomás</t>
@@ -6548,7 +6530,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>Pestszentlőrinc vasútállomás</t>
@@ -6581,7 +6562,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>Pestszentlőrinc vasútállomás</t>
@@ -6614,7 +6594,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>Pestszentlőrinc vasútállomás</t>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G169"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -6610,6 +6610,598 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F170" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F171" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G171" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SGY806</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>47.441998, 19.072416</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PDN627</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F173" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F174" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G174" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>47.409943, 19.060173</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F176" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G176" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SGY807</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>47.427177, 19.070105</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>0660</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>AOGF651</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>47.45776, 19.071344</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>AAHY866</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Bogáncs telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>AAMH603</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>0975</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>AOJM886</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F183" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G183" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>AAHY867</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Bogáncs telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>AAMH678</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F185" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G185" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -7202,6 +7202,598 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F186" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G186" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F187" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G187" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SGY818</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PDN618</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F189" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G189" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F190" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G190" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F191" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G191" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F192" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G192" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SGY810</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F193" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G193" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0660</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>AOJM883</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F196" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G196" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>AAHY804</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F197" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G197" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>AAMH603</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Bogáncs telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>0975</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>AOJM886</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F199" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G199" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>AAHY820</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F200" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G200" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>AAMH658</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F201" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G201" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -7794,6 +7794,598 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F202" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G202" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F203" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G203" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SGY816</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F205" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G205" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F206" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G206" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>47.409927, 19.060137</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F208" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G208" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SGY810</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F209" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G209" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>0660</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>AOIM012</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>AOGF671</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F212" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G212" s="1" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>AAHY820</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F213" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G213" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>AAMH603</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Bogáncs telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>0975</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>AOJM886</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F215" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G215" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>AAHY869</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F216" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G216" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>AAMH674</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F217" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G217" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Aptos Narrow"/>
       <charset val="238"/>
@@ -29,8 +29,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="004DA3FF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +54,11 @@
     <fill>
       <patternFill patternType="solid"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B9BD5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -63,11 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -465,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G217"/>
+  <dimension ref="A1:G233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -8386,6 +8397,598 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F218" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G218" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F219" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G219" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SGY809</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F221" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G221" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F222" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G222" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>47.40996, 19.060186</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>AOGF659</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G224" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SGY810</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F225" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G225" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>0660</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>AOGF651</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>AOJM868</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>AAHY845</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>AAMH603</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Bogáncs telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>0975</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>AOCT668</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (dél</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Bogáncs telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>AAMH673</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F233" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G233" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/hidegtarolas_export.xlsx
+++ b/data/hidegtarolas_export.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G233"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -8989,6 +8989,598 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>0960</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>AAHY878</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F234" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G234" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>AAHY812</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Békásmegyer, Újmegyeri tér</t>
+        </is>
+      </c>
+      <c r="F235" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G235" s="1" t="inlineStr">
+        <is>
+          <t>Békásmegyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SGY821</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PDN625</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F237" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G237" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>PDN623</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F238" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G238" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>AOIM009</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>AOGF674</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F240" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G240" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SGY810</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+      <c r="F241" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G241" s="1" t="inlineStr">
+        <is>
+          <t>Csepel, Szent Imre tér</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>0660</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>AOGF651</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Szállító telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>AOIM010</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Pestszentlőrinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>AOGF658</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Kőbánya-Kispest M (Sibrik tároló)</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Kőbánya alsó</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>AAHY845</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F245" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G245" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>AAMH603</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>ArrivaBus Bogáncs telephely</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>0975</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>AOCT668</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (dél</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>AAHY853</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G248" s="1" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (észak</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>AADR755</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Örs vezér tere M+H (északi tároló)</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
